--- a/inputData/inputDataMicro.xlsx
+++ b/inputData/inputDataMicro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4828C538-0B6E-4FA3-8EFD-75A7A6D78DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA23A94-C39E-2142-9278-35646F6FAD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23420" windowHeight="16000" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="8" r:id="rId1"/>
@@ -58,15 +58,9 @@
     <t>(55.629053, 12.647601)</t>
   </si>
   <si>
-    <t>(55.740278, 9.151667)</t>
-  </si>
-  <si>
     <t>københavn</t>
   </si>
   <si>
-    <t>billund</t>
-  </si>
-  <si>
     <t>group</t>
   </si>
   <si>
@@ -98,6 +92,12 @@
   </si>
   <si>
     <t>minuts/unit</t>
+  </si>
+  <si>
+    <t>(55.7003, 11.2500)</t>
+  </si>
+  <si>
+    <t>kalundborg</t>
   </si>
 </sst>
 </file>
@@ -186,7 +186,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -510,20 +510,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -539,13 +539,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -556,10 +556,10 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -573,33 +573,33 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D6" s="1"/>
     </row>
   </sheetData>
@@ -611,32 +611,32 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -656,16 +656,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" s="3">
         <f>[1]Parameters!$B$20</f>
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
